--- a/review/2026-10-brand-decisions.xlsx
+++ b/review/2026-10-brand-decisions.xlsx
@@ -13,7 +13,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'廠牌決策'!$A$1:$J$53</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'廠牌決策'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'產品清單（參考）'!$A$1:$E$232</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'產品清單（參考）'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -576,7 +578,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -853,7 +855,17 @@
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B8:C8"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.45" right="0.45" top="0.7" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"微軟正黑體,Regular"&amp;9 &amp;K5B6B7C耕紋貿易官網｜代理廠牌現況確認表</oddHeader>
+    <oddFooter>&amp;R&amp;"微軟正黑體,Regular"&amp;9 &amp;K5B6B7C第 &amp;P 頁，共 &amp;N 頁</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -861,7 +873,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2700,7 +2712,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId52"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.45" right="0.45" top="0.7" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"微軟正黑體,Regular"&amp;9 &amp;K5B6B7C耕紋貿易官網｜代理廠牌現況確認表</oddHeader>
+    <oddFooter>&amp;R&amp;"微軟正黑體,Regular"&amp;9 &amp;K5B6B7C第 &amp;P 頁，共 &amp;N 頁</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -2709,7 +2731,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9220,6 +9242,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E231" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E232" r:id="rId231"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.45" right="0.45" top="0.7" bottom="0.6" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"微軟正黑體,Regular"&amp;9 &amp;K5B6B7C耕紋貿易官網｜代理廠牌現況確認表</oddHeader>
+    <oddFooter>&amp;R&amp;"微軟正黑體,Regular"&amp;9 &amp;K5B6B7C第 &amp;P 頁，共 &amp;N 頁</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>